--- a/web/templates/template-siswa.xlsx
+++ b/web/templates/template-siswa.xlsx
@@ -1,21 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyWebApp\Proyek\Production\GuruAksi\web\templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF40BD73-0036-4F24-9186-1440F7C55BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>NISN</t>
   </si>
@@ -38,24 +43,27 @@
     <t>NoTelp</t>
   </si>
   <si>
-    <t>NamaAyah</t>
-  </si>
-  <si>
-    <t>NamaIbu</t>
-  </si>
-  <si>
-    <t>TahunMasuk</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>TmpLahir</t>
+  </si>
+  <si>
+    <t>TglLahir</t>
+  </si>
+  <si>
+    <t>Agama</t>
   </si>
   <si>
     <t>0012345678</t>
   </si>
   <si>
+    <t>2024001</t>
+  </si>
+  <si>
     <t>Ahmad Fatoni</t>
   </si>
   <si>
-    <t>VII A</t>
-  </si>
-  <si>
     <t>L</t>
   </si>
   <si>
@@ -65,15 +73,24 @@
     <t>081234567890</t>
   </si>
   <si>
-    <t>Budi Santoso</t>
-  </si>
-  <si>
-    <t>Siti Aminah</t>
+    <t>ahmad@email.com</t>
+  </si>
+  <si>
+    <t>Jakarta</t>
+  </si>
+  <si>
+    <t>2010-05-10</t>
+  </si>
+  <si>
+    <t>Islam</t>
   </si>
   <si>
     <t>0012345679</t>
   </si>
   <si>
+    <t>2024002</t>
+  </si>
+  <si>
     <t>Siti Nurhaliza</t>
   </si>
   <si>
@@ -86,34 +103,49 @@
     <t>081234567891</t>
   </si>
   <si>
-    <t>Joko Widodo</t>
-  </si>
-  <si>
-    <t>Mega Sari</t>
+    <t>siti@email.com</t>
+  </si>
+  <si>
+    <t>Bandung</t>
+  </si>
+  <si>
+    <t>2010-08-15</t>
+  </si>
+  <si>
+    <t>7 A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <b val="0"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0891B2"/>
+        <bgColor rgb="FF0891B2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -128,14 +160,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -214,7 +258,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -249,7 +292,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -425,124 +467,130 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.854" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="6.998" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="13.997" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="14" style="2" customWidth="1"/>
+    <col min="2" max="2" width="11" style="2" customWidth="1"/>
+    <col min="3" max="3" width="18" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19" style="2" customWidth="1"/>
+    <col min="7" max="7" width="16" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <v>2024001</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2">
-        <v>2024</v>
+      <c r="I2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3">
-        <v>2024002</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3">
-        <v>2024</v>
       </c>
     </row>
   </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>